--- a/tests/fixtures/31_date_types/31_date_types_pattern-from-nvidia.xlsx
+++ b/tests/fixtures/31_date_types/31_date_types_pattern-from-nvidia.xlsx
@@ -510,7 +510,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-03-15 00:00:00</t>
+          <t>2026-03-15</t>
         </is>
       </c>
     </row>
